--- a/ABM/raw_data/non_chebba_sites_areas.xlsx
+++ b/ABM/raw_data/non_chebba_sites_areas.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alvar\Repository\Roman-Chebba-agriculture\ABM\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE5B3814-F86C-44B4-B1A4-B9460E17F286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4375A809-4E09-4107-ADF2-3916F4DEAE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FD69D61B-0B9E-4A42-8884-2BB0B43A1F17}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A9F174B-A2A1-4CBC-8B62-8BA1CB03E714}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet1!#REF!, Sheet1!#REF!</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet1!#REF!, Sheet1!$A:$A</definedName>
   </definedNames>
-  <calcPr calcId="80000"/>
+  <calcPr calcId="80000" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="39">
   <si>
     <t>ID</t>
   </si>
@@ -52,9 +52,6 @@
     <t>Area (ha)</t>
   </si>
   <si>
-    <t>Eddouamis</t>
-  </si>
-  <si>
     <t>El Kherba</t>
   </si>
   <si>
@@ -127,27 +124,12 @@
     <t>Henchir Echbilette</t>
   </si>
   <si>
-    <t>Biar Ali Ben Mosbah</t>
-  </si>
-  <si>
     <t>Henchir El Merigueb</t>
   </si>
   <si>
     <t>Oued Awinet al Hjal</t>
   </si>
   <si>
-    <t>Henchir El Hanichate</t>
-  </si>
-  <si>
-    <t>Sidi Amor Ben Bouzid</t>
-  </si>
-  <si>
-    <t>Bir El Araba (Essaguia)</t>
-  </si>
-  <si>
-    <t>74.078–74.080</t>
-  </si>
-  <si>
     <t>Henchir l’Abbasi</t>
   </si>
   <si>
@@ -158,9 +140,6 @@
   </si>
   <si>
     <t>Sidi al Khafi / Henchir Sidi al Khafi</t>
-  </si>
-  <si>
-    <t>Henchir Ben Maati / Henchir Ben Mustapha</t>
   </si>
 </sst>
 </file>
@@ -176,20 +155,17 @@
       <sz val="12"/>
       <color indexed="23"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color indexed="8"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -239,15 +215,15 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -584,17 +560,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE18A0E6-CC2D-452B-905E-6094F9D499AC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8501468-D56A-4341-8E4E-D2C1F1BA982C}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="11.28515625" customWidth="1"/>
-    <col min="3" max="3" width="51.7109375" customWidth="1"/>
-    <col min="4" max="5" width="11.28515625" customWidth="1"/>
-    <col min="6" max="234" width="9.140625" customWidth="1"/>
+    <col min="1" max="3" width="14.140625" customWidth="1"/>
+    <col min="4" max="29" width="11.28515625" customWidth="1"/>
+    <col min="30" max="256" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -622,7 +597,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -633,282 +608,282 @@
     </row>
     <row r="3" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>74.028000000000006</v>
+        <v>74.034999999999997</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3">
         <v>1</v>
       </c>
       <c r="E3" s="3">
-        <v>35</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>74.034999999999997</v>
+        <v>74.036000000000001</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
       </c>
       <c r="E4" s="3">
-        <v>2</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>74.036000000000001</v>
+        <v>74.186000000000007</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
       </c>
       <c r="E5" s="3">
-        <v>0.16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>74.186000000000007</v>
+        <v>74.22</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
       </c>
       <c r="E6" s="3">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>74.22</v>
+        <v>43.131</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D7" s="3">
         <v>1</v>
       </c>
       <c r="E7" s="3">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>43.131</v>
+        <v>43.021999999999998</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D8" s="3">
         <v>1</v>
       </c>
       <c r="E8" s="3">
-        <v>1.18</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>43.021999999999998</v>
+        <v>43.024000000000001</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="D9" s="3">
         <v>1</v>
       </c>
       <c r="E9" s="3">
-        <v>2.93</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>43.024000000000001</v>
+        <v>43.034999999999997</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
       </c>
       <c r="E10" s="3">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>43.034999999999997</v>
+        <v>43.09</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
       </c>
       <c r="E11" s="3">
-        <v>1.26</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>43.09</v>
+        <v>43.158999999999999</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D12" s="3">
         <v>1</v>
       </c>
       <c r="E12" s="3">
-        <v>2.6</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>43.158999999999999</v>
+        <v>72.063999999999993</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
       </c>
       <c r="E13" s="3">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>72.072999999999993</v>
+        <v>72.128</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
       </c>
       <c r="E14" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>72.063999999999993</v>
+        <v>64.025999999999996</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
       </c>
       <c r="E15" s="3">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>72.128</v>
+        <v>64.055999999999997</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D16" s="3">
         <v>1</v>
       </c>
       <c r="E16" s="3">
-        <v>1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>72.016999999999996</v>
+        <v>64.070999999999998</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="D17" s="3">
         <v>1</v>
       </c>
       <c r="E17" s="3">
-        <v>4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>72.132999999999996</v>
+        <v>64.066999999999993</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="D18" s="3">
         <v>1</v>
       </c>
       <c r="E18" s="3">
-        <v>3</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>64.025999999999996</v>
+        <v>64.11</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>1</v>
@@ -921,410 +896,274 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <v>64.055999999999997</v>
+      <c r="A20" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D20" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="3">
-        <v>0.3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>64.070999999999998</v>
+        <v>74.031000000000006</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D21" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="3">
-        <v>0.2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
-        <v>64.066999999999993</v>
+      <c r="A22" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D22" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="3">
-        <v>0.08</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>64.11</v>
+        <v>43.012999999999998</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="D23" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="3">
-        <v>0.6</v>
+        <v>12.67</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>75.042000000000002</v>
+        <v>43.029000000000003</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D24" s="3">
         <v>2</v>
       </c>
       <c r="E24" s="3">
-        <v>25</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>21</v>
+      <c r="A25" s="1">
+        <v>43.033999999999999</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D25" s="3">
         <v>2</v>
       </c>
       <c r="E25" s="3">
-        <v>10</v>
+        <v>10.029999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>40</v>
+      <c r="A26" s="1">
+        <v>43.037999999999997</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D26" s="3">
         <v>2</v>
       </c>
       <c r="E26" s="3">
-        <v>50</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>74.031000000000006</v>
+        <v>43.137</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D27" s="3">
         <v>2</v>
       </c>
       <c r="E27" s="3">
-        <v>10</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
-        <v>18</v>
+      <c r="A28" s="1">
+        <v>43.179000000000002</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D28" s="3">
         <v>2</v>
       </c>
       <c r="E28" s="3">
-        <v>10</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
-        <v>43.012999999999998</v>
+        <v>43.180999999999997</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D29" s="3">
         <v>2</v>
       </c>
       <c r="E29" s="3">
-        <v>12.67</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
-        <v>43.029000000000003</v>
+        <v>72.061000000000007</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D30" s="3">
         <v>2</v>
       </c>
       <c r="E30" s="3">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
-        <v>43.033999999999999</v>
+        <v>72.051000000000002</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D31" s="3">
         <v>2</v>
       </c>
       <c r="E31" s="3">
-        <v>10.029999999999999</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
-        <v>43.037999999999997</v>
+        <v>72.087000000000003</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D32" s="3">
         <v>2</v>
       </c>
       <c r="E32" s="3">
-        <v>3.49</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
-        <v>43.137</v>
+        <v>72.114000000000004</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D33" s="3">
         <v>2</v>
       </c>
       <c r="E33" s="3">
-        <v>5.95</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
-        <v>43.179000000000002</v>
+        <v>64.007000000000005</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D34" s="3">
         <v>2</v>
       </c>
       <c r="E34" s="3">
-        <v>5.58</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
-        <v>43.180999999999997</v>
+        <v>64.072999999999993</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D35" s="3">
         <v>2</v>
       </c>
       <c r="E35" s="3">
-        <v>3.98</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="1">
-        <v>72.061000000000007</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D36" s="3">
-        <v>2</v>
-      </c>
-      <c r="E36" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="1">
-        <v>72.051000000000002</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D37" s="3">
-        <v>2</v>
-      </c>
-      <c r="E37" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="1">
-        <v>72.087000000000003</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D38" s="3">
-        <v>2</v>
-      </c>
-      <c r="E38" s="3">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="1">
-        <v>72.114000000000004</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D39" s="3">
-        <v>2</v>
-      </c>
-      <c r="E39" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="1">
-        <v>64.054000000000002</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D40" s="3">
-        <v>2</v>
-      </c>
-      <c r="E40" s="3">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="1">
-        <v>64.075999999999993</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D41" s="3">
-        <v>2</v>
-      </c>
-      <c r="E41" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="1">
-        <v>64.007000000000005</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D42" s="3">
-        <v>2</v>
-      </c>
-      <c r="E42" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="1">
-        <v>64.072999999999993</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D43" s="3">
-        <v>2</v>
-      </c>
-      <c r="E43" s="3">
         <v>3</v>
       </c>
     </row>

--- a/ABM/raw_data/non_chebba_sites_areas.xlsx
+++ b/ABM/raw_data/non_chebba_sites_areas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alvar\Repository\Roman-Chebba-agriculture\ABM\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4375A809-4E09-4107-ADF2-3916F4DEAE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91560920-569E-45F0-9E50-9573042B4723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4A9F174B-A2A1-4CBC-8B62-8BA1CB03E714}"/>
   </bookViews>
@@ -18,12 +18,12 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Sheet1!#REF!, Sheet1!$A:$A</definedName>
   </definedNames>
-  <calcPr calcId="80000" fullCalcOnLoad="1"/>
+  <calcPr calcId="80000"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="42">
   <si>
     <t>ID</t>
   </si>
@@ -140,6 +140,15 @@
   </si>
   <si>
     <t>Sidi al Khafi / Henchir Sidi al Khafi</t>
+  </si>
+  <si>
+    <t>Edduoamis</t>
+  </si>
+  <si>
+    <t>Henchir el hachinate</t>
+  </si>
+  <si>
+    <t>75 Mahdia</t>
   </si>
 </sst>
 </file>
@@ -186,7 +195,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -209,21 +218,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -564,7 +592,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="14.140625" customWidth="1"/>
@@ -1167,6 +1195,61 @@
         <v>3</v>
       </c>
     </row>
+    <row r="36" spans="1:5" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="A36" s="4">
+        <v>75.042000000000002</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="5">
+        <v>2</v>
+      </c>
+      <c r="E36" s="5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="34.5" x14ac:dyDescent="0.2">
+      <c r="B37" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" s="5">
+        <v>2</v>
+      </c>
+      <c r="E37" s="5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="D38" s="5">
+        <v>1</v>
+      </c>
+      <c r="E38" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="D39" s="5">
+        <v>1</v>
+      </c>
+      <c r="E39" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="D40" s="5">
+        <v>1</v>
+      </c>
+      <c r="E40" s="5">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
